--- a/calendars/source/syllabus.xlsx
+++ b/calendars/source/syllabus.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A58DDA-CD5C-49C1-B1D5-089561845421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC98B9B-6EC6-4513-9030-7D9F51F8ADE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hermeneutics (BudHerm)" sheetId="1" r:id="rId1"/>
     <sheet name="Śūraṅgama (Śūraṅgama)" sheetId="2" r:id="rId2"/>
     <sheet name="Sanskrit (संस्कृत)" sheetId="3" r:id="rId3"/>
-    <sheet name="Yogācāra (Yogācāra)" sheetId="4" r:id="rId4"/>
+    <sheet name="Yogācāra (Yogācāra)" sheetId="6" r:id="rId4"/>
     <sheet name="_Recurring" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="166">
   <si>
     <t>date</t>
   </si>
@@ -64,33 +64,6 @@
   </si>
   <si>
     <t>Exam</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Waldron’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Making Sense of Mind Only </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>[chapter 4 to the end] </t>
-    </r>
   </si>
   <si>
     <t>The Story of Gotama Buddha: The Nidāna-kathā of the Jātakaṭṭhakathā</t>
@@ -122,36 +95,6 @@
   </si>
   <si>
     <t>Hallisey, Charles, Trans. Therīgāthā: Poems of The First Buddhist Women. Cambridge: Harvard Univ, 2015. (Selections)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(Thirty Verses) </t>
-    </r>
   </si>
   <si>
     <t>Grant, Beata. Daughters of Emptiness: Poems of Chinese 
@@ -268,1432 +211,9 @@
     <t>Student presentations / contemplative exercise</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Ācārya Vasubandhu’s Thirty Verses (Triṁśikā)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">, tr. and explained by Mattia Salvini based  on Sthiramati’s commentary. Read the verses carefully (reader) and skim the commentary  (pp. 20-119 </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>https://d3zr9vspdnjxi.cloudfront.net/sites/saugata1/sup/7739033--c-rya Vasubandhu-s-Thirty-Verses-Tri-ik-A-Manual-for-Students-2022.pdf</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>) as needed. This is  an introductory framework for the whole semester. You don’t need to master everything  this week. We will unpack these verses during the rest of the semester. </t>
-    </r>
-  </si>
-  <si>
-    <t>Yogācāra’s goal </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 1-2 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Laṅkāvatārasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pages 71-83, 90-93, and 181-5 (LXIV) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 2, pages 509-515 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Xuanzang’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Three Texts on Consciousness Only </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">chap. 1, pages 9-20, 39-43, and 298-302 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF222222"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(Verses 1-2ab) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Laukikamārga </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">(mundane path) of the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Śrāvakabhūmi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>vol. 2 (=</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Yogācārabhūmi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>), pages 446- 452 </t>
-    </r>
-  </si>
-  <si>
-    <t>ālaya </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 2-5a </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">The Scripture on the Explication of Underlying Meaning </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Saṃdhinirmocana Sūtra</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>) pages  27-29 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Asaṅga’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">The Summary of the Great Vehicle </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Mahāyānasaṃgraha</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>) chapter 1 pages 13-36 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Pravṛtti </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">and </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Nivṛtti Portions </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">of the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Viniścayasaṃgrahaṇī </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">of the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Yogācārabhūmi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">in  Waldron’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">The Buddhist Unconscious </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pages 178-89 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Pañcaskandaka </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>with Sthiramati’s commentary “The Consciousness Heap” pages 327-344  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Saṃdhinirmocana Sūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 6, pages 51-55 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">ālaya </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(cont.) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 2cd-4 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Xuanzang’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Three Texts on Consciousness Only </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapters 2-3 (Verses 2cd-4), pp. 47-111 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Maitreya’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Distinguishing the Middle from the Extremes </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Madhyāntavibhāgabhāṣyam</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>)  pages 176-77 </t>
-    </r>
-  </si>
-  <si>
-    <t>kliṣṭamanas </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 5-8a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Paramārthagāthās </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">1-27 and 42-44 (tr. Wayman) and 28-41 and their commentary (tr.  Schmithausen) from the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Yogācārabhūmi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pages 335-341 and 229-241, respectively </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Pañcaskandhaka </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>with Sthiramati’s commentary “The Afflicted Mind” pages 344-47 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Xuanzang’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Three Texts on Consciousness Only </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 4, pages 113-122, 128-132, 137- 140, 142-144 (Verse 5-7) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">The Questions of King Milinda </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>2.1.1 pages 40-45  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 2, pages 503-505 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pravṛttivijñāna</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>s </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 8b-16 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Xuanzang’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Three Texts on Consciousness Only </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 5, pages 153-161 (Verses 8-9),  164-169 (Verse 10), 172-181 (Verse 11), 185-189 (Verse 12ab), 196-205 (Verse 12cd 14ab), 210-212 (Verse 14cd), 219-229 (Verses 15-16) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Asaṅga’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Mahāyānasaṃgraha </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>page 11 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pravṛttivijñāna</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>s (cont.) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 17-20 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">MN 140 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Chadhātuvibhāṅgasutta </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 2, pages 343-455  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Optional: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(Vol 2), Appendix 4, pages 222-301 CE: four foundations of mindfulness with dependent arising</t>
-    </r>
-  </si>
-  <si>
-    <t>three natures </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 20-28</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Maitreya and Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">chapter 1, pages 117-130 Asaṅga’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Mahāyānasaṃgraha </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapters 2-3, pages 37-70 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Vasubandhu’s “The Three Natures Exposition” (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Trisvabhāvanirdeśaḥ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">) pages 244-248 Maitreya and Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>page 178-183 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">🡪 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>quick in-class paper topic check in</t>
-    </r>
-  </si>
-  <si>
-    <t>three natures (cont.) </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 20-28 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Maitreya and Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 3, pages 143-159 </t>
-    </r>
-  </si>
-  <si>
-    <t>Brennan’s “The Three Natures and the Path to Liberation in Yogācāra-Vijñānavāda  Thought” </t>
-  </si>
-  <si>
-    <t>Waldron’s “A Yogācārin approach to Collective Illusions: Cultural Unconscious, Implicit  Bias and Racism without Races” </t>
-  </si>
-  <si>
-    <t>Bayo Akomolafe’s “Dear White People” </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">practicing </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">vijñaptimātratā </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>on the bodhisattva path </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Asaṅga’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Mahāyānasaṃgraha </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 4, pages 71-77 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Maitreya and Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 4, pages 161-172 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Bodhisattvabhūmi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(=</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Yogācārabhūmi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">) in </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">The Bodhisattva Path to Unsurpassed  Enlightenment </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pages 402-413 and 450-463 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">stages and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pāramitā</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>s on the bodhisattva path </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verse 29  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Asaṅga’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Mahāyānasaṃgraha </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapters 5-9, pages 79-101; optional: </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Saṃdhinirmocanasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">chapter 7, pages 77-98, and </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Śūraṅgama Sūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">pages 329-43 Xuanzang’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Three Texts on Consciousness Only </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">chapter 11, pages 313-323 (verse 29) </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">The Interpretation of the Buddha Land </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pages 193-195 </t>
-    </r>
-  </si>
-  <si>
     <t>(paper due by 5pm – upload to Google Classroom)</t>
   </si>
   <si>
-    <t>obstacles on the path and concepts related to liberation </t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -1709,33 +229,6 @@
     <t>end_date</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Triṃśikā </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>verses 29-30 </t>
-    </r>
-  </si>
-  <si>
     <t>every_n_weeks</t>
   </si>
   <si>
@@ -1751,197 +244,18 @@
     <t>BudHerm</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Maitreya and Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">chapter 2, pages 131-141 Xuanzang’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Three Texts on Consciousness Only </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">chapter 11, pages 323-40 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 2, pages 525-527 </t>
-    </r>
-  </si>
-  <si>
     <t>Journal entry</t>
   </si>
   <si>
     <t>Sunday</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Laṅkāvatārasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">pages 256-61; optional: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Saṃdhinirmocanasūtra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">chapter 8, pp 99-112 Asaṅga’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Mahāyānasaṃgraha </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapter 10, pages 103-119 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Xuanzang’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Three Texts on Consciousness Only </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>chapters 12-14, pages 341-367 (verses  29-30) </t>
-    </r>
-  </si>
-  <si>
     <t>TRUE</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">The Interpretation of the Buddha Land </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>pages 12-13, 19-20, 24-25, 107-111 CE: the pure land as the mind of wisdom, as “pure conscious construction”</t>
-    </r>
-  </si>
-  <si>
     <t>Weekly Question</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Vasubandhu’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Twenty Verses </t>
-    </r>
-  </si>
-  <si>
     <t>Tuesday</t>
   </si>
   <si>
@@ -2006,6 +320,243 @@
   </si>
   <si>
     <t>Friday</t>
+  </si>
+  <si>
+    <t>Waldron’s Making Sense of Mind Only [chapter 4 to the end]</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā (Thirty Verses)</t>
+  </si>
+  <si>
+    <t>Ācārya Vasubandhu’s Thirty Verses (Triṁśikā), tr. and explained by Mattia Salvini based on Sthiramati’s commentary. Read the verses carefully (reader) and skim the commentary (pp. 20-119) as needed. This is an introductory framework for the whole semester. You don’t need to master everything this week. We will unpack these verses during the rest of the semester.</t>
+  </si>
+  <si>
+    <t>Yogācāra’s goal</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verses 1-2</t>
+  </si>
+  <si>
+    <t>Laṅkāvatārasūtra pages 71-83, 90-93, and 181-5 (LXIV)</t>
+  </si>
+  <si>
+    <t>Saddharmasmṛtyupasthānasūtra chapter 2, pages 509-515</t>
+  </si>
+  <si>
+    <t>Xuanzang’s Three Texts on Consciousness Only chap. 1, pages 9-20, 39-43, and 298-302 (Verses 1-2ab)</t>
+  </si>
+  <si>
+    <t>Laukikamārga (mundane path) of the Śrāvakabhūmi vol. 2 (=Yogācārabhūmi), pages 446-452</t>
+  </si>
+  <si>
+    <t>ālaya</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verses 2-5a</t>
+  </si>
+  <si>
+    <t>The Scripture on the Explication of Underlying Meaning (Saṃdhinirmocana Sūtra) pages 27-29</t>
+  </si>
+  <si>
+    <t>Asaṅga’s The Summary of the Great Vehicle (Mahāyānasaṃgraha) chapter 1 pages 13-36</t>
+  </si>
+  <si>
+    <t>Pravṛtti and Nivṛtti Portions of the Viniścayasaṃgrahaṇī of the Yogācārabhūmi in Waldron’s The Buddhist Unconscious pages 178-89</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Pañcaskandaka with Sthiramati’s commentary “The Consciousness Heap” pages 327-344</t>
+  </si>
+  <si>
+    <t>Saṃdhinirmocana Sūtra chapter 6, pages 51-55</t>
+  </si>
+  <si>
+    <t>ālaya (cont.)</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verses 2cd-4</t>
+  </si>
+  <si>
+    <t>Xuanzang’s Three Texts on Consciousness Only chapters 2-3 (Verses 2cd-4), pp. 47-111</t>
+  </si>
+  <si>
+    <t>Maitreya’s Distinguishing the Middle from the Extremes (Madhyāntavibhāgabhāṣyam) pages 176-77</t>
+  </si>
+  <si>
+    <t>kliṣṭamanas</t>
+  </si>
+  <si>
+    <t>🌱 TNH — Transformation at the Base, Part II “Manas”: ch. 16 Seeds of Delusion (91) · 17 Mentation (94) · 18 The Mark of a Self (98) · 19 The Ground of Wholesome and Unwholesome (104) · 20 Companions of Manas (108) · 21 Manas Always Follows Store Consciousness (112) · 22 Release (114). Book pp. 91-118 = PDF pp. 105-132</t>
+  </si>
+  <si>
+    <t>🌱 TNH catch-up — Transformation at the Base: Introduction (bk 1-7 / PDF 15-21); the Fifty Verses in full (bk 9-18 / PDF 23-32); Part I “Store Consciousness,” ch. 1-15 (bk 21-88 / PDF 35-102) — re-skim, previously read; may carry over into 10/8</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verses 5-8a</t>
+  </si>
+  <si>
+    <t>Paramārthagāthās 1-27 and 42-44 (tr. Wayman) and 28-41 and their commentary (tr. Schmithausen) from the Yogācārabhūmi pages 335-341 and 229-241, respectively</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Pañcaskandhaka with Sthiramati’s commentary “The Afflicted Mind” pages 344-47</t>
+  </si>
+  <si>
+    <t>Xuanzang’s Three Texts on Consciousness Only chapter 4, pages 113-122, 128-132, 137-140, 142-144 (Verse 5-7)</t>
+  </si>
+  <si>
+    <t>The Questions of King Milinda 2.1.1 pages 40-45</t>
+  </si>
+  <si>
+    <t>Saddharmasmṛtyupasthānasūtra chapter 2, pages 503-505</t>
+  </si>
+  <si>
+    <t>pravṛttivijñānas</t>
+  </si>
+  <si>
+    <t>🌱 TNH — Transformation at the Base, Part III “Mind Consciousness”: ch. 23 Sphere of Cognition (121) · 24 Perception (123) · 25 The Gardener (133) · 26 Non-Perception (136) · 27 States of Mind (139). Book pp. 121-142 = PDF pp. 135-156</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verses 8b-16</t>
+  </si>
+  <si>
+    <t>Xuanzang’s Three Texts on Consciousness Only chapter 5, pages 153-161 (Verses 8-9), 164-169 (Verse 10), 172-181 (Verse 11), 185-189 (Verse 12ab), 196-205 (Verse 12cd 14ab), 210-212 (Verse 14cd), 219-229 (Verses 15-16)</t>
+  </si>
+  <si>
+    <t>Asaṅga’s Mahāyānasaṃgraha page 11</t>
+  </si>
+  <si>
+    <t>pravṛttivijñānas (cont.)</t>
+  </si>
+  <si>
+    <t>🌱 TNH — Transformation at the Base, Part IV “Sense Consciousnesses” and the opening of Part V: ch. 28 Waves upon the Water (145) · 29 Direct Perception (148) · 30 Mental Formations (152) · 31 Subject and Object (157) · 32 Perceiver, Perceived, and Wholeness (164) · 33 Birth and Death (168). Book pp. 145-170 = PDF pp. 159-184</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verses 17-20</t>
+  </si>
+  <si>
+    <t>MN 140 Chadhātuvibhāṅgasutta</t>
+  </si>
+  <si>
+    <t>Saddharmasmṛtyupasthānasūtra chapter 2, pages 343-455</t>
+  </si>
+  <si>
+    <t>Optional: Saddharmasmṛtyupasthānasūtra (Vol 2), Appendix 4, pages 222-301 CE: four foundations of mindfulness with dependent arising</t>
+  </si>
+  <si>
+    <t>three natures</t>
+  </si>
+  <si>
+    <t>🌱 TNH — Transformation at the Base, Part V “The Nature of Reality”: ch. 34 Continuous Manifestation (171) · 35 Ripening (177) · 36 No Coming, No Going (181) · 37 Causes (184) · 38 Conditions (186). Book pp. 171-187 = PDF pp. 185-201 — his paratantra material</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verses 20-28</t>
+  </si>
+  <si>
+    <t>Maitreya and Vasubandhu’s Madhyāntavibhāgabhāṣyam chapter 1, pages 117-130</t>
+  </si>
+  <si>
+    <t>Asaṅga’s Mahāyānasaṃgraha chapters 2-3, pages 37-70</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s “The Three Natures Exposition” (Trisvabhāvanirdeśaḥ) pages 244-248</t>
+  </si>
+  <si>
+    <t>Maitreya and Vasubandhu’s Madhyāntavibhāgabhāṣyam pages 178-183</t>
+  </si>
+  <si>
+    <t>🡪 quick in-class paper topic check in</t>
+  </si>
+  <si>
+    <t>three natures (cont.)</t>
+  </si>
+  <si>
+    <t>🌱 TNH — Transformation at the Base, Part V concluded: ch. 39 True Mind (188) · 40 Constructed, Interdependent, and Fulfilled Nature (193). Book pp. 188-194 = PDF pp. 202-208 — ch. 40 is his direct treatment of the trisvabhāva; short but the bullseye for this week</t>
+  </si>
+  <si>
+    <t>Maitreya and Vasubandhu’s Madhyāntavibhāgabhāṣyam chapter 3, pages 143-159</t>
+  </si>
+  <si>
+    <t>Brennan’s “The Three Natures and the Path to Liberation in Yogācāra-Vijñānavāda Thought”</t>
+  </si>
+  <si>
+    <t>Waldron’s “A Yogācārin approach to Collective Illusions: Cultural Unconscious, Implicit Bias and Racism without Races”</t>
+  </si>
+  <si>
+    <t>Bayo Akomolafe’s “Dear White People”</t>
+  </si>
+  <si>
+    <t>practicing vijñaptimātratā on the bodhisattva path</t>
+  </si>
+  <si>
+    <t>🌱 TNH — Transformation at the Base, Part VI “The Path of Practice”: ch. 41 The Way to Practice (197) · 42 Flower and Garbage (205) · 43 Interbeing (208) · 44 Right View (211). Book pp. 197-213 = PDF pp. 211-227</t>
+  </si>
+  <si>
+    <t>Asaṅga’s Mahāyānasaṃgraha chapter 4, pages 71-77</t>
+  </si>
+  <si>
+    <t>Maitreya and Vasubandhu’s Madhyāntavibhāgabhāṣyam chapter 4, pages 161-172</t>
+  </si>
+  <si>
+    <t>Bodhisattvabhūmi (=Yogācārabhūmi) in The Bodhisattva Path to Unsurpassed Enlightenment pages 402-413 and 450-463</t>
+  </si>
+  <si>
+    <t>stages and pāramitās on the bodhisattva path</t>
+  </si>
+  <si>
+    <t>🌱 TNH — Transformation at the Base: ch. 45 Mindfulness (214) · 46 Transformation at the Base (219) · 47 The Present Moment (226). Book pp. 214-231 = PDF pp. 228-245 — ch. 46 is āśrayaparāvṛtti, i.e. Triṃśikā v. 29</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verse 29</t>
+  </si>
+  <si>
+    <t>Asaṅga’s Mahāyānasaṃgraha chapters 5-9, pages 79-101; optional</t>
+  </si>
+  <si>
+    <t>Saṃdhinirmocanasūtra chapter 7, pages 77-98, and Śūraṅgama Sūtra pages 329-43</t>
+  </si>
+  <si>
+    <t>Xuanzang’s Three Texts on Consciousness Only chapter 11, pages 313-323 (verse 29)</t>
+  </si>
+  <si>
+    <t>The Interpretation of the Buddha Land pages 193-195</t>
+  </si>
+  <si>
+    <t>obstacles on the path and concepts related to liberation</t>
+  </si>
+  <si>
+    <t>🌱 TNH — Transformation at the Base, close of Part VI: ch. 48 Sangha (232) · 49 Nothing to Attain (237) · 50 Non-Fear (241). Book pp. 232-242 = PDF pp. 246-256 — ch. 49 is his anupalambha chapter, directly on Triṃśikā 28-30</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Triṃśikā verses 29-30</t>
+  </si>
+  <si>
+    <t>Maitreya and Vasubandhu’s Madhyāntavibhāgabhāṣyam chapter 2, pages 131-141</t>
+  </si>
+  <si>
+    <t>Xuanzang’s Three Texts on Consciousness Only chapter 11, pages 323-340</t>
+  </si>
+  <si>
+    <t>Saddharmasmṛtyupasthānasūtra chapter 2, pages 525-527</t>
+  </si>
+  <si>
+    <t>Laṅkāvatārasūtra pages 256-261</t>
+  </si>
+  <si>
+    <t>Optional: Saṃdhinirmocanasūtra chapter 8, pages 99-112</t>
+  </si>
+  <si>
+    <t>Asaṅga’s Mahāyānasaṃgraha chapter 10, pages 103-119</t>
+  </si>
+  <si>
+    <t>Xuanzang’s Three Texts on Consciousness Only chapters 12-14, pages 341-367 (verses 29-30)</t>
+  </si>
+  <si>
+    <t>The Interpretation of the Buddha Land pages 12-13, 19-20, 24-25, 107-111 CE: the pure land as the mind of wisdom, as “pure conscious construction”</t>
+  </si>
+  <si>
+    <t>Vasubandhu’s Twenty Verses</t>
+  </si>
+  <si>
+    <t>🌱 TNH capstone — Transformation at the Base: re-read the Fifty Verses straight through in one sitting, bk pp. 9-18 = PDF pp. 23-32. The only deliberate re-read in the plan; by now every verse has a commentary behind it</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +566,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2077,17 +628,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2479,7 +1019,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2490,7 +1030,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2501,7 +1041,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2512,7 +1052,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2523,7 +1063,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2534,7 +1074,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2545,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2553,10 +1093,10 @@
         <v>46287</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2567,7 +1107,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2578,7 +1118,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2589,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2600,7 +1140,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2611,7 +1151,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2622,7 +1162,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2630,10 +1170,10 @@
         <v>46315</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2644,7 +1184,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2655,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2666,7 +1206,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2677,7 +1217,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2688,7 +1228,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2699,7 +1239,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2707,10 +1247,10 @@
         <v>46357</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2718,10 +1258,10 @@
         <v>46364</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3875,7 +2415,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3886,7 +2426,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3897,7 +2437,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3908,7 +2448,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3919,7 +2459,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3930,7 +2470,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3941,7 +2481,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3952,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3963,7 +2503,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3974,7 +2514,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3985,7 +2525,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3996,7 +2536,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -4007,7 +2547,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -4018,7 +2558,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -5211,7 +3751,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -5222,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -5233,7 +3773,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -5244,7 +3784,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6484,7 +5024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763832FE-DE87-4B38-A625-8844E934FE87}">
   <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6493,7 +5033,7 @@
     <col min="4" max="26" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6504,7 +5044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>46254</v>
       </c>
@@ -6512,744 +5052,647 @@
         <v>3</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <v>46261</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
-        <f>A3</f>
         <v>46261</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
-        <v>46268</v>
+        <v>46261</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
-        <f t="shared" ref="A6:A10" si="0">A5</f>
-        <v>46268</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
-        <f t="shared" si="0"/>
         <v>46268</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
-        <f t="shared" si="0"/>
         <v>46268</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
-        <f t="shared" si="0"/>
         <v>46268</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
-        <f t="shared" si="0"/>
         <v>46268</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
-        <f t="shared" ref="A12:A17" si="1">A11</f>
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <f t="shared" si="1"/>
-        <v>46275</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>61</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
-        <f t="shared" si="1"/>
         <v>46275</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
-        <f t="shared" si="1"/>
         <v>46275</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
-        <f t="shared" si="1"/>
         <v>46275</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
-        <f t="shared" si="1"/>
         <v>46275</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
-        <f t="shared" ref="A19:A21" si="2">A18</f>
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
-        <f t="shared" si="2"/>
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
-        <f t="shared" si="2"/>
-        <v>46282</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>69</v>
-      </c>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="10"/>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
-        <f t="shared" ref="A23:A28" si="3">A22</f>
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
-        <f t="shared" si="3"/>
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
-        <f t="shared" si="3"/>
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3">
-        <f t="shared" si="3"/>
-        <v>46289</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>74</v>
-      </c>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="10"/>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
-        <f t="shared" si="3"/>
         <v>46289</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
-        <f t="shared" si="3"/>
         <v>46289</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
-        <v>46303</v>
+        <v>46289</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
-        <f t="shared" ref="A30:A32" si="4">A29</f>
-        <v>46303</v>
+        <v>46289</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
-        <f t="shared" si="4"/>
-        <v>46303</v>
+        <v>46289</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
-        <f t="shared" si="4"/>
-        <v>46303</v>
+        <v>46289</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
-        <v>46310</v>
+        <v>46289</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
-        <f t="shared" ref="A34:A37" si="5">A33</f>
-        <v>46310</v>
+        <v>46289</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
-        <f t="shared" si="5"/>
-        <v>46310</v>
+        <v>46289</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3">
-        <f t="shared" si="5"/>
-        <v>46310</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="9"/>
+    </row>
+    <row r="37" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3">
-        <f t="shared" si="5"/>
-        <v>46310</v>
+        <v>46303</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
-        <v>46317</v>
+        <v>46303</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
-        <f t="shared" ref="A39:A42" si="6">A38</f>
-        <v>46317</v>
+        <v>46303</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
-        <f t="shared" si="6"/>
-        <v>46317</v>
+        <v>46303</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
-        <f t="shared" si="6"/>
-        <v>46317</v>
+        <v>46303</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="3">
-        <f t="shared" si="6"/>
-        <v>46317</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>90</v>
-      </c>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="14"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
-        <v>46324</v>
+        <v>46310</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
-        <f t="shared" ref="A44:A48" si="7">A43</f>
-        <v>46324</v>
+        <v>46310</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
-        <f t="shared" si="7"/>
-        <v>46324</v>
+        <v>46310</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
-        <f t="shared" si="7"/>
-        <v>46324</v>
+        <v>46310</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
-        <f t="shared" si="7"/>
-        <v>46324</v>
+        <v>46310</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="3">
-        <f t="shared" si="7"/>
-        <v>46324</v>
+        <v>46310</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="3">
-        <v>46331</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="7"/>
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
-        <f t="shared" ref="A50:A52" si="8">A49</f>
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
-        <f t="shared" si="8"/>
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
-        <f t="shared" si="8"/>
-        <v>46331</v>
+        <v>46317</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
-        <v>46338</v>
+        <v>46317</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
-        <f t="shared" ref="A54:A57" si="9">A53</f>
-        <v>46338</v>
+        <v>46317</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
-        <f t="shared" si="9"/>
-        <v>46338</v>
+        <v>46317</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
-        <f t="shared" si="9"/>
-        <v>46338</v>
+        <v>46317</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
-        <f t="shared" si="9"/>
-        <v>46338</v>
+        <v>46317</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="3">
-        <v>46359</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>106</v>
-      </c>
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="7"/>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
-        <f t="shared" ref="A59:A63" si="10">A58</f>
-        <v>46359</v>
+        <v>46324</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
-        <f t="shared" si="10"/>
-        <v>46359</v>
+        <v>46324</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
-        <f t="shared" si="10"/>
-        <v>46359</v>
+        <v>46324</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
-        <f t="shared" si="10"/>
-        <v>46359</v>
+        <v>46324</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3">
-        <f t="shared" si="10"/>
-        <v>46359</v>
+        <v>46324</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
-        <v>46366</v>
+        <v>46324</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="22"/>
+      <c r="A65" s="3">
+        <v>46324</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="66" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
@@ -7257,29 +5700,59 @@
       <c r="C66" s="22"/>
     </row>
     <row r="67" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="22"/>
+      <c r="A67" s="3">
+        <v>46331</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="68" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="22"/>
+      <c r="A68" s="3">
+        <v>46331</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="69" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="22"/>
+      <c r="A69" s="3">
+        <v>46331</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="70" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="22"/>
+      <c r="A70" s="3">
+        <v>46331</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="71" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="22"/>
+      <c r="A71" s="3">
+        <v>46331</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="72" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
@@ -7287,44 +5760,92 @@
       <c r="C72" s="22"/>
     </row>
     <row r="73" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="22"/>
+      <c r="A73" s="3">
+        <v>46338</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="74" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="22"/>
+      <c r="A74" s="3">
+        <v>46338</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="75" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="22"/>
+      <c r="A75" s="3">
+        <v>46338</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="76" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="22"/>
+      <c r="A76" s="3">
+        <v>46338</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="77" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="22"/>
+      <c r="A77" s="3">
+        <v>46338</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="22" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="78" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="22"/>
+      <c r="A78" s="3">
+        <v>46338</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="22" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="79" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="22"/>
+      <c r="A79" s="3">
+        <v>46338</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="22" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="80" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="22"/>
+      <c r="A80" s="3">
+        <v>46338</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="81" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
@@ -7332,59 +5853,125 @@
       <c r="C81" s="22"/>
     </row>
     <row r="82" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="22"/>
+      <c r="A82" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="22" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="83" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="22"/>
+      <c r="A83" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C83" s="22" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="84" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="22"/>
+      <c r="A84" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="22" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="85" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="22"/>
+      <c r="A85" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" s="22" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="86" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="22"/>
+      <c r="A86" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="22" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="87" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="22"/>
+      <c r="A87" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="88" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="22"/>
+      <c r="A88" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C88" s="22" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="89" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="22"/>
+      <c r="A89" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="90" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="22"/>
+      <c r="A90" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C90" s="22" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="91" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="22"/>
+      <c r="A91" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C91" s="22" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="92" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="22"/>
+      <c r="A92" s="3">
+        <v>46359</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="22" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="93" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
@@ -7392,14 +5979,26 @@
       <c r="C93" s="22"/>
     </row>
     <row r="94" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="22"/>
+      <c r="A94" s="3">
+        <v>46366</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" s="22" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="95" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="22"/>
+      <c r="A95" s="3">
+        <v>46366</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="96" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
@@ -11952,7 +10551,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -11961,42 +10560,42 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="E2" s="16">
         <v>0.91666666666666663</v>
@@ -12011,23 +10610,23 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="E3" s="16">
         <v>0.75</v>
@@ -12042,21 +10641,21 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="E4" s="16">
         <v>0.99930555555555556</v>
@@ -12071,21 +10670,21 @@
         <v>2</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="E5" s="25">
         <v>0.29166666666666669</v>
@@ -12105,16 +10704,16 @@
     </row>
     <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="23" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="E6" s="25">
         <v>0.29166666666666669</v>
@@ -12134,16 +10733,16 @@
     </row>
     <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="E7" s="25">
         <v>0.29166666666666669</v>
@@ -12163,16 +10762,16 @@
     </row>
     <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="23" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="E8" s="25">
         <v>0.29166666666666669</v>
@@ -12192,16 +10791,16 @@
     </row>
     <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="23" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="E9" s="25">
         <v>0.29166666666666669</v>
@@ -12236,65 +10835,65 @@
     </row>
     <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="24" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="23" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="23" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="23" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="23" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="23" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="23" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="23" t="s">
-        <v>135</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="23" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="23" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="23" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="23" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/calendars/source/syllabus.xlsx
+++ b/calendars/source/syllabus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC98B9B-6EC6-4513-9030-7D9F51F8ADE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C20644-9A8C-42E4-A2E0-C30F778C37A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hermeneutics (BudHerm)" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="167">
   <si>
     <t>date</t>
   </si>
@@ -557,6 +557,9 @@
   </si>
   <si>
     <t>🌱 TNH capstone — Transformation at the Base: re-read the Fifty Verses straight through in one sitting, bk pp. 9-18 = PDF pp. 23-32. The only deliberate re-read in the plan; by now every verse has a commentary behind it</t>
+  </si>
+  <si>
+    <t>Custom</t>
   </si>
 </sst>
 </file>
@@ -10681,7 +10684,7 @@
         <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>65</v>
@@ -10710,7 +10713,7 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>84</v>
@@ -10739,7 +10742,7 @@
         <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>85</v>
@@ -10768,7 +10771,7 @@
         <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>86</v>
@@ -10797,7 +10800,7 @@
         <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>62</v>
